--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-electronics-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-electronics-easy.xlsx
@@ -460,19 +460,19 @@
         <v>Định luật Ohm là nền tảng điện tử: Cường độ dòng điện chạy qua vật dẫn tỷ lệ thuận với hiệu điện thế giữa hai đầu vật dẫn và tỷ lệ nghịch với điện trở của vật dẫn.</v>
       </c>
       <c r="F2" t="str">
+        <v>Điện dung của tụ (C), Điện tích (Q), Điện áp (V) bằng công thức $Q = C \cdot V$ — công thức điện tích tụ</v>
+      </c>
+      <c r="G2" t="str">
         <v>Cường độ dòng điện (I), Điện áp (V), Điện trở (R) bằng công thức $I = V / R$ — định luật Ohm</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Công suất (P), Điện năng (W), Thời gian (t) bằng công thức $P = W / t$ — công thức công suất</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Điện dung của tụ (C), Điện tích (Q), Điện áp (V) bằng công thức $Q = C \cdot V$ — công thức điện tích tụ</v>
       </c>
       <c r="I2" t="str">
         <v>Từ thông (Phi), Độ tự cảm (L), Dòng điện (I) bằng công thức $Phi = L \cdot I$ — công thức từ thông cuộn cảm</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Điện trở (R, đơn vị Ohm) dùng để hạn dòng (tránh cháy LED/cháy chân chip) hoặc phân áp (Voltage divider).</v>
       </c>
       <c r="F3" t="str">
-        <v>Cản trở dòng điện để giới hạn dòng hoặc phân chia điện áp trong mạch — cản trở dòng điện</v>
+        <v>Cho phép dòng điện chỉ chạy qua theo một chiều duy nhất và chặn chiều ngược lại — van điện một chiều</v>
       </c>
       <c r="G3" t="str">
         <v>Lưu trữ năng lượng dưới dạng điện trường giữa hai bản cực song song — tích lũy năng lượng điện trường</v>
       </c>
       <c r="H3" t="str">
-        <v>Cho phép dòng điện chỉ chạy qua theo một chiều duy nhất và chặn chiều ngược lại — van điện một chiều</v>
+        <v>Cản trở dòng điện để giới hạn dòng hoặc phân chia điện áp trong mạch — cản trở dòng điện</v>
       </c>
       <c r="I3" t="str">
         <v>Đóng cắt mạch điện tự động dựa trên tín hiệu điều khiển của nam châm điện — công tắc điện từ</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Tụ điện (C, đơn vị Farad) cho dòng AC đi qua (để lọc nhiễu xoay chiều tần số cao xuống đất) và chặn dòng DC. Nó nạp xả năng lượng giúp ổn định điện áp nguồn cấp.</v>
       </c>
       <c r="F4" t="str">
+        <v>Cản trở dòng điện xoay chiều và cho dòng điện một chiều đi qua dễ dàng — chặn dòng xoay chiều</v>
+      </c>
+      <c r="G4" t="str">
         <v>Tích lũy năng lượng điện trường, lọc nhiễu nguồn điện và chặn dòng điện một chiều (DC) — tích lũy điện trường lọc nguồn</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Tự động tăng điện áp dòng điện xoay chiều lên gấp 10 lần — tăng điện áp xoay chiều</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Cản trở dòng điện xoay chiều và cho dòng điện một chiều đi qua dễ dàng — chặn dòng xoay chiều</v>
       </c>
       <c r="I4" t="str">
         <v>Đóng ngắt mạch điện tự động khi dòng điện vượt quá giới hạn cho phép — bảo vệ quá dòng</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -559,10 +559,10 @@
         <v>Cho phép dòng điện chạy qua theo một chiều từ Anode sang Cathode và chặn chiều ngược lại — van điện một chiều</v>
       </c>
       <c r="G5" t="str">
+        <v>Biến đổi dòng điện một chiều thành dòng điện xoay chiều tần số cao — nghịch lưu</v>
+      </c>
+      <c r="H5" t="str">
         <v>Tích lũy năng lượng dưới dạng từ trường khi có dòng điện chạy qua — cuộn cảm</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Biến đổi dòng điện một chiều thành dòng điện xoay chiều tần số cao — nghịch lưu</v>
       </c>
       <c r="I5" t="str">
         <v>Tự động ngắt kết nối mạch điện khi nhiệt độ môi trường xung quanh tăng cao — rơ-le nhiệt</v>
@@ -588,19 +588,19 @@
         <v>Khi nút bấm mở (chưa nhấn), nếu không có điện trở kéo (Pull-up/Pull-down), chân GPIO sẽ ở trạng thái lơ lửng (floating). Nhiễu điện từ xung quanh có thể làm chân tự động nhảy giữa High và Low, khiến MCU đọc sai trạng thái. Điện trở kéo (thường là 10k Ohm) giúp ghim chân về mức điện áp xác định.</v>
       </c>
       <c r="F6" t="str">
+        <v>Nối trực tiếp chân GPIO đó xuống đất GND bằng một sợi dây đồng — nối đất trực tiếp chân chip</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Một chiếc diode Zener mắc song song với nút bấm — diode Zener bảo vệ áp</v>
+      </c>
+      <c r="H6" t="str">
         <v>Điện trở kéo lên (Pull-up Resistor) nối lên nguồn VCC hoặc điện trở kéo xuống (Pull-down Resistor) nối xuống đất GND — mạch điện trở kéo ổn định trạng thái</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>Một cuộn cảm có độ tự cảm lớn nối tiếp với nút bấm — cuộn cảm hạn dòng ngắt</v>
       </c>
-      <c r="H6" t="str">
-        <v>Một chiếc diode Zener mắc song song với nút bấm — diode Zener bảo vệ áp</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Nối trực tiếp chân GPIO đó xuống đất GND bằng một sợi dây đồng — nối đất trực tiếp chân chip</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Vạn năng kế (đồng hồ đo điện) là dụng cụ cơ bản của kỹ sư nhúng để đo điện áp (AC/DC), dòng điện và điện trở, thông mạch.</v>
       </c>
       <c r="F7" t="str">
+        <v>Tần số sóng vô tuyến Wi-Fi và cường độ sóng điện từ trường — đo sóng vô tuyến</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Số lượng bóng bán dẫn bị hỏng bên trong con chip vi điều khiển — quét lỗi IC</v>
+      </c>
+      <c r="H7" t="str">
         <v>Điện áp (Voltage), Cường độ dòng điện (Current), và Điện trở (Resistance) — vạn năng đo U I R</v>
       </c>
-      <c r="G7" t="str">
-        <v>Tần số sóng vô tuyến Wi-Fi và cường độ sóng điện từ trường — đo sóng vô tuyến</v>
-      </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>Độ dày của lớp đồng trên bảng mạch in PCB và nhiệt độ lò hàn — đo cơ học nhiệt độ</v>
       </c>
-      <c r="I7" t="str">
-        <v>Số lượng bóng bán dẫn bị hỏng bên trong con chip vi điều khiển — quét lỗi IC</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Oscilloscope giúp kỹ sư nhúng nhìn thấy tín hiệu điện thực tế (xung clock, tín hiệu UART, nhiễu nguồn), đo tần số, biên độ và sườn xung.</v>
       </c>
       <c r="F8" t="str">
+        <v>Nạp chương trình code từ máy tính vào trong bộ nhớ Flash của chip — mạch nạp chương trình</v>
+      </c>
+      <c r="G8" t="str">
         <v>Trực quan hóa đồ thị dạng sóng của điện áp thay đổi theo thời gian trên màn hình hiển thị — trực quan hóa dạng sóng điện áp</v>
       </c>
-      <c r="G8" t="str">
-        <v>Nạp chương trình code từ máy tính vào trong bộ nhớ Flash của chip — mạch nạp chương trình</v>
-      </c>
       <c r="H8" t="str">
+        <v>Đo lường dung lượng pin còn lại của thiết bị di động di động — đo dung lượng pin</v>
+      </c>
+      <c r="I8" t="str">
         <v>Hàn các linh kiện điện tử dán SMD lên bảng mạch in PCB — trạm hàn linh kiện</v>
       </c>
-      <c r="I8" t="str">
-        <v>Đo lường dung lượng pin còn lại của thiết bị di động di động — đo dung lượng pin</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>LED là Diode phát quang. Khi phân cực thuận, các electron tái hợp với lỗ trống trong chất bán dẫn giải phóng năng lượng dưới dạng photon ánh sáng.</v>
       </c>
       <c r="F9" t="str">
-        <v>Là một loại diode đặc biệt phát ra ánh sáng khi có dòng điện chạy qua theo chiều thuận từ Anode sang Cathode — LED phát sáng</v>
+        <v>Sử dụng sợi đốt vonfram nung nóng ở nhiệt độ cao để phát sáng — bóng đèn sợi đốt</v>
       </c>
       <c r="G9" t="str">
-        <v>Sử dụng sợi đốt vonfram nung nóng ở nhiệt độ cao để phát sáng — bóng đèn sợi đốt</v>
+        <v>Biến đổi trực tiếp ánh sáng mặt trời thành dòng điện một chiều nạp vào pin — pin mặt trời</v>
       </c>
       <c r="H9" t="str">
         <v>Tích năng lượng điện trường rồi tự phát sáng vào ban đêm không cần dòng điện — phát quang tự thân</v>
       </c>
       <c r="I9" t="str">
-        <v>Biến đổi trực tiếp ánh sáng mặt trời thành dòng điện một chiều nạp vào pin — pin mặt trời</v>
+        <v>Là một loại diode đặc biệt phát ra ánh sáng khi có dòng điện chạy qua theo chiều thuận từ Anode sang Cathode — LED phát sáng</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>Traces (Đường mạch dẫn) — các đường đồng dẫn điện trên PCB — traces đường mạch đồng</v>
       </c>
       <c r="G10" t="str">
+        <v>Pads (Chân hàn) — các vị trí đồng để đặt thiếc hàn chân linh kiện — pads chân hàn linh kiện</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Silkscreen (Lớp in chữ) — lớp in ký hiệu linh kiện màu trắng trên mạch — silkscreen in ký hiệu</v>
+      </c>
+      <c r="I10" t="str">
         <v>Vias (Lỗ thông tầng) — các lỗ nối mạch giữa các lớp đồng khác nhau — vias lỗ thông tầng</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Pads (Chân hàn) — các vị trí đồng để đặt thiếc hàn chân linh kiện — pads chân hàn linh kiện</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Silkscreen (Lớp in chữ) — lớp in ký hiệu linh kiện màu trắng trên mạch — silkscreen in ký hiệu</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -748,19 +748,19 @@
         <v>LED có đặc tuyến Volt-Ampere phi tuyến. Khi điện áp vượt quá điện áp thuận ($V_f$), dòng tăng vọt theo hàm mũ. Mắc nối tiếp điện trở giúp gánh phần điện áp dư ($V_R = 5V - V_f$) và giới hạn dòng điện an toàn (thường 10-20mA).</v>
       </c>
       <c r="F11" t="str">
+        <v>Để tăng độ sáng của đèn LED lên mức tối đa để nhìn rõ hơn — tăng độ sáng LED</v>
+      </c>
+      <c r="G11" t="str">
         <v>Vì LED có điện trở nội cực kỳ nhỏ; không có điện trở hạn dòng sẽ gây ra dòng điện quá lớn chạy qua làm cháy LED ngay lập tức — hạn dòng bảo vệ LED</v>
       </c>
-      <c r="G11" t="str">
-        <v>Để tăng độ sáng của đèn LED lên mức tối đa để nhìn rõ hơn — tăng độ sáng LED</v>
-      </c>
       <c r="H11" t="str">
+        <v>Vì nếu không có điện trở, LED sẽ tự động đổi màu sắc hiển thị liên tục — đổi màu LED</v>
+      </c>
+      <c r="I11" t="str">
         <v>Để chuyển đổi dòng điện một chiều sang dòng điện xoay chiều cấp cho LED — chuyển đổi dòng điện</v>
       </c>
-      <c r="I11" t="str">
-        <v>Vì nếu không có điện trở, LED sẽ tự động đổi màu sắc hiển thị liên tục — đổi màu LED</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
